--- a/⚙️T'Z0C Card Catalog.xlsx
+++ b/⚙️T'Z0C Card Catalog.xlsx
@@ -113,14 +113,13 @@
         <sz val="12.0"/>
         <u/>
       </rPr>
-      <t>https://github.com/Titantus/Truth-Zero-C/blob/main/TZ0C_Lab_v5.ipynb</t>
+      <t>https://github.com/Titantus/Truth-Zero-C</t>
     </r>
     <r>
       <rPr>
         <rFont val="Google Sans"/>
         <color rgb="FF000000"/>
         <sz val="12.0"/>
-        <u/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
